--- a/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QA-GEN-MBKAT-TDAMF-RCA-1</t>
+          <t>QA-GEN-MBKAT-4O4S5-RCA-1</t>
         </is>
       </c>
     </row>

--- a/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QA-GEN-MBKAT-4O4S5-RCA-1</t>
+          <t>QA-GEN-MBKAT-ISN36-RCA-1</t>
         </is>
       </c>
     </row>

--- a/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
+++ b/Wikidata Delta/qa_gen_excels/pep_qatar_living_relevant_rca_lookup.xlsx
@@ -832,7 +832,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>QA-GEN-MBKAT-ISN36-RCA-1</t>
+          <t>QA-GEN-MBKAT-9W2UE-RCA-1</t>
         </is>
       </c>
     </row>
